--- a/sitepreview/pcmt/StructureDefinition-ProductID.xlsx
+++ b/sitepreview/pcmt/StructureDefinition-ProductID.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-25T13:01:38+00:00</t>
+    <t>2025-06-26T06:31:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
